--- a/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
+++ b/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC17" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Norway_Eli" displayName="AveragesTable_Norway_Eli" ref="A1:EC17" headerRowCount="1">
   <autoFilter ref="A1:EC17"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
+++ b/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
         <v>0.36</v>
@@ -2275,52 +2275,52 @@
         <v>0.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AI4" t="n">
-        <v>113.64</v>
+        <v>106.07</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AL4" t="n">
-        <v>7.57</v>
+        <v>7.73</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AN4" t="n">
-        <v>71</v>
+        <v>66.27</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.93</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.21</v>
+        <v>10.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.21</v>
+        <v>6.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>61.5</v>
+        <v>62.8</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA4" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.71</v>
+        <v>10.53</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.79</v>
+        <v>5.87</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.57</v>
+        <v>18.33</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.86</v>
+        <v>10.97</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="BK4" t="n">
         <v>0.79</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BM4" t="n">
         <v>0.79</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.32</v>
+        <v>5.48</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.29</v>
+        <v>5.24</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>89.29000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="BT4" t="n">
-        <v>71.43000000000001</v>
+        <v>72.41</v>
       </c>
       <c r="BU4" t="n">
-        <v>46.43</v>
+        <v>44.83</v>
       </c>
       <c r="BV4" t="n">
-        <v>28.57</v>
+        <v>27.59</v>
       </c>
       <c r="BW4" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BX4" t="n">
-        <v>57.14</v>
+        <v>58.62</v>
       </c>
       <c r="BY4" t="n">
         <v>1.24</v>
@@ -2416,55 +2416,55 @@
         <v>1.28</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.08</v>
+        <v>6.02</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.74</v>
+        <v>6.69</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CG4" t="n">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.63</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CM4" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CO4" t="n">
         <v>1.09</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
@@ -2476,7 +2476,7 @@
         <v>3.32</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CV4" t="n">
         <v>2.34</v>
@@ -2485,16 +2485,16 @@
         <v>1.68</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DB4" t="n">
         <v>1.14</v>
@@ -2503,82 +2503,82 @@
         <v>1.41</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="DH4" t="n">
-        <v>111.5</v>
+        <v>107.66</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="DK4" t="n">
-        <v>7.82</v>
+        <v>7.89</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="DM4" t="n">
-        <v>79.34999999999999</v>
+        <v>76.62</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="DP4" t="n">
-        <v>8.460000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10.21</v>
+        <v>9.93</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.64</v>
+        <v>5.48</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>63.22</v>
+        <v>63.83</v>
       </c>
       <c r="DW4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX4" t="n">
-        <v>18.18</v>
+        <v>18.07</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.86</v>
+        <v>11.72</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.33</v>
+        <v>6.35</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.28</v>
+        <v>18.65</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="5">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
         <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F8" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="H8" t="n">
-        <v>105.5</v>
+        <v>98.47</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="K8" t="n">
-        <v>4.86</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="M8" t="n">
-        <v>58.86</v>
+        <v>54.93</v>
       </c>
       <c r="N8" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>11.71</v>
+        <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.57</v>
+        <v>8.93</v>
       </c>
       <c r="R8" t="n">
-        <v>6.43</v>
+        <v>6</v>
       </c>
       <c r="S8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>16.47</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.43</v>
       </c>
-      <c r="T8" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>51.93</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>13.07</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AF8" t="n">
         <v>0.07000000000000001</v>
@@ -3971,67 +3971,67 @@
         <v>2.79</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.710000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="BI8" t="n">
         <v>2.79</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.71</v>
+        <v>4.9</v>
       </c>
       <c r="BQ8" t="n">
         <v>4</v>
       </c>
       <c r="BR8" t="n">
-        <v>89.29000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="BS8" t="n">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>51.72</v>
       </c>
       <c r="BU8" t="n">
-        <v>39.29</v>
+        <v>37.93</v>
       </c>
       <c r="BV8" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>60.71</v>
+        <v>62.07</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.69</v>
+        <v>3.74</v>
       </c>
       <c r="CC8" t="n">
         <v>3.64</v>
@@ -4040,124 +4040,124 @@
         <v>3.98</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI8" t="n">
         <v>1.9</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CK8" t="n">
         <v>1.52</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM8" t="n">
         <v>2.43</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="CR8" t="n">
         <v>1.45</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CT8" t="n">
         <v>2.89</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY8" t="n">
         <v>1.98</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DA8" t="n">
         <v>1.84</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DH8" t="n">
-        <v>99.43000000000001</v>
+        <v>96</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="DM8" t="n">
-        <v>48.04</v>
+        <v>46.38</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.36</v>
+        <v>11.52</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.43</v>
+        <v>10.07</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.61</v>
+        <v>6.38</v>
       </c>
       <c r="DS8" t="n">
         <v>0.07000000000000001</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.64</v>
+        <v>49.55</v>
       </c>
       <c r="DW8" t="n">
         <v>0.1</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.46</v>
+        <v>11.28</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.6</v>
+        <v>7.45</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.04</v>
+        <v>17.48</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
         <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AI9" t="n">
-        <v>78.64</v>
+        <v>78.27</v>
       </c>
       <c r="AJ9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.14</v>
+        <v>4.27</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>33.64</v>
+        <v>33.73</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AP9" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.43</v>
+        <v>9.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.36</v>
+        <v>10.53</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.79</v>
+        <v>10.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>40.29</v>
+        <v>40.4</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.93</v>
+        <v>10.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.57</v>
+        <v>6.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>20.21</v>
+        <v>19.53</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.07</v>
+        <v>3.17</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.36</v>
+        <v>10.38</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.07</v>
+        <v>3.17</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.29</v>
+        <v>4.31</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.86</v>
+        <v>4.9</v>
       </c>
       <c r="BR9" t="n">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.56999999999999</v>
+        <v>79.31</v>
       </c>
       <c r="BT9" t="n">
-        <v>57.14</v>
+        <v>58.62</v>
       </c>
       <c r="BU9" t="n">
-        <v>39.29</v>
+        <v>41.38</v>
       </c>
       <c r="BV9" t="n">
-        <v>21.43</v>
+        <v>24.14</v>
       </c>
       <c r="BW9" t="n">
-        <v>10.71</v>
+        <v>13.79</v>
       </c>
       <c r="BX9" t="n">
-        <v>60.71</v>
+        <v>62.07</v>
       </c>
       <c r="BY9" t="n">
         <v>3.19</v>
@@ -4431,25 +4431,25 @@
         <v>3.44</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.68</v>
+        <v>5.56</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.39</v>
+        <v>6.28</v>
       </c>
       <c r="CE9" t="n">
         <v>1.28</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CH9" t="n">
         <v>1.6</v>
@@ -4467,10 +4467,10 @@
         <v>1.59</v>
       </c>
       <c r="CM9" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CO9" t="n">
         <v>1.16</v>
@@ -4479,25 +4479,25 @@
         <v>1.58</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CT9" t="n">
         <v>3.16</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX9" t="n">
         <v>1.47</v>
@@ -4518,82 +4518,82 @@
         <v>1.62</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="DE9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="DH9" t="n">
-        <v>85.42</v>
+        <v>85</v>
       </c>
       <c r="DI9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="DM9" t="n">
-        <v>39.04</v>
+        <v>38.9</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DP9" t="n">
-        <v>9.640000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.39</v>
+        <v>10.48</v>
       </c>
       <c r="DR9" t="n">
-        <v>10.43</v>
+        <v>10.45</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.04</v>
+        <v>43</v>
       </c>
       <c r="DW9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.82</v>
+        <v>11.03</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.07</v>
+        <v>7.17</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.75</v>
+        <v>3.86</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.96</v>
+        <v>19.62</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="10">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
         <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
         <v>0.07000000000000001</v>
@@ -5096,52 +5096,52 @@
         <v>1.43</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AI11" t="n">
-        <v>76.29000000000001</v>
+        <v>72.53</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.93</v>
+        <v>4.73</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>42.57</v>
+        <v>41.4</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.64</v>
+        <v>11.53</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.14</v>
+        <v>13.27</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.86</v>
+        <v>8.07</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AV11" t="n">
         <v>0.07000000000000001</v>
@@ -5153,82 +5153,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.79</v>
+        <v>48.47</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA11" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>6.87</v>
       </c>
       <c r="BC11" t="n">
-        <v>4</v>
+        <v>3.73</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.29</v>
+        <v>18.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.93</v>
+        <v>10.79</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.64</v>
+        <v>4.59</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.61</v>
+        <v>4.52</v>
       </c>
       <c r="BR11" t="n">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>82.14</v>
+        <v>79.31</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>48.28</v>
       </c>
       <c r="BU11" t="n">
-        <v>35.71</v>
+        <v>34.48</v>
       </c>
       <c r="BV11" t="n">
-        <v>21.43</v>
+        <v>20.69</v>
       </c>
       <c r="BW11" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="BX11" t="n">
-        <v>53.57</v>
+        <v>51.72</v>
       </c>
       <c r="BY11" t="n">
         <v>1.74</v>
@@ -5237,16 +5237,16 @@
         <v>1.92</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.76</v>
+        <v>3.01</v>
       </c>
       <c r="CE11" t="n">
         <v>1.3</v>
@@ -5255,16 +5255,16 @@
         <v>2.38</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK11" t="n">
         <v>1.35</v>
@@ -5273,16 +5273,16 @@
         <v>1.69</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ11" t="n">
         <v>2.54</v>
@@ -5291,82 +5291,82 @@
         <v>1.38</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CU11" t="n">
         <v>1.56</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CW11" t="n">
         <v>1.68</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DB11" t="n">
         <v>1.22</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="DE11" t="n">
         <v>0.14</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="DH11" t="n">
-        <v>86.25</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ11" t="n">
         <v>2.14</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.28</v>
+        <v>6.13</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM11" t="n">
-        <v>49.04</v>
+        <v>48.21</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.22</v>
+        <v>11.17</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.18</v>
+        <v>13.24</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.93</v>
+        <v>7.07</v>
       </c>
       <c r="DS11" t="n">
         <v>0.18</v>
@@ -5378,25 +5378,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52.68</v>
+        <v>52.86</v>
       </c>
       <c r="DW11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.78</v>
+        <v>12.52</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.57</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.22</v>
+        <v>4.07</v>
       </c>
       <c r="EA11" t="n">
         <v>19.72</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="EC11" t="n">
         <v>2</v>
@@ -6614,94 +6614,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="F15" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="G15" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="H15" t="n">
-        <v>97</v>
+        <v>91.67</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="K15" t="n">
-        <v>4.21</v>
+        <v>4.27</v>
       </c>
       <c r="L15" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="M15" t="n">
-        <v>50</v>
+        <v>48.73</v>
       </c>
       <c r="N15" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="O15" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="P15" t="n">
-        <v>13.71</v>
+        <v>13.8</v>
       </c>
       <c r="Q15" t="n">
         <v>9.93</v>
       </c>
       <c r="R15" t="n">
-        <v>7</v>
+        <v>6.93</v>
       </c>
       <c r="S15" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="T15" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="U15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>52.43</v>
+        <v>51.73</v>
       </c>
       <c r="Y15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.71</v>
+        <v>12.87</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.07</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>18.36</v>
+        <v>18.53</v>
       </c>
       <c r="AD15" t="n">
         <v>1.49</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AF15" t="n">
         <v>0.36</v>
@@ -6785,70 +6785,70 @@
         <v>1.57</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.710000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.14</v>
+        <v>4.07</v>
       </c>
       <c r="BR15" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS15" t="n">
-        <v>67.86</v>
+        <v>65.52</v>
       </c>
       <c r="BT15" t="n">
-        <v>53.57</v>
+        <v>51.72</v>
       </c>
       <c r="BU15" t="n">
-        <v>42.86</v>
+        <v>41.38</v>
       </c>
       <c r="BV15" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="BW15" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="BX15" t="n">
-        <v>53.57</v>
+        <v>51.72</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="CC15" t="n">
         <v>3.01</v>
@@ -6857,13 +6857,13 @@
         <v>3.2</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CH15" t="n">
         <v>1.47</v>
@@ -6875,10 +6875,10 @@
         <v>1.75</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM15" t="n">
         <v>2.7</v>
@@ -6893,13 +6893,13 @@
         <v>1.81</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CT15" t="n">
         <v>3.14</v>
@@ -6908,73 +6908,73 @@
         <v>1.48</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW15" t="n">
         <v>1.8</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB15" t="n">
         <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="DH15" t="n">
-        <v>100.15</v>
+        <v>97.28</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="DM15" t="n">
-        <v>48.57</v>
+        <v>47.96</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.07</v>
+        <v>13.14</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.43</v>
+        <v>10.41</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.46</v>
+        <v>7.41</v>
       </c>
       <c r="DS15" t="n">
         <v>0.14</v>
@@ -6986,28 +6986,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>50.14</v>
+        <v>49.86</v>
       </c>
       <c r="DW15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.71</v>
+        <v>11.83</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.43</v>
+        <v>7.52</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.28</v>
+        <v>4.31</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.07</v>
+        <v>19.14</v>
       </c>
       <c r="EB15" t="n">
         <v>1.4</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="16">
@@ -7420,61 +7420,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
         <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F17" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="H17" t="n">
-        <v>90</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="K17" t="n">
-        <v>6.21</v>
+        <v>6.13</v>
       </c>
       <c r="L17" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="M17" t="n">
-        <v>53.57</v>
+        <v>53</v>
       </c>
       <c r="N17" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="P17" t="n">
-        <v>12.29</v>
+        <v>12.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>12.93</v>
       </c>
       <c r="R17" t="n">
-        <v>8.57</v>
+        <v>8.4</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="U17" t="n">
         <v>0.07000000000000001</v>
@@ -7486,28 +7486,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>48.93</v>
+        <v>49.53</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.07</v>
+        <v>16.87</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.14</v>
+        <v>11</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.93</v>
+        <v>5.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.07</v>
+        <v>20.73</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF17" t="n">
         <v>0.14</v>
@@ -7591,64 +7591,64 @@
         <v>1.64</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="BH17" t="n">
-        <v>11.32</v>
+        <v>11.31</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.61</v>
+        <v>4.62</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.11</v>
+        <v>6.1</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>85.70999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>57.14</v>
+        <v>58.62</v>
       </c>
       <c r="BU17" t="n">
-        <v>35.71</v>
+        <v>37.93</v>
       </c>
       <c r="BV17" t="n">
-        <v>25</v>
+        <v>27.59</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.14</v>
+        <v>10.34</v>
       </c>
       <c r="BX17" t="n">
-        <v>64.29000000000001</v>
+        <v>65.52</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="CA17" t="n">
         <v>3.92</v>
@@ -7666,10 +7666,10 @@
         <v>1.28</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CH17" t="n">
         <v>1.58</v>
@@ -7687,10 +7687,10 @@
         <v>1.58</v>
       </c>
       <c r="CM17" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CO17" t="n">
         <v>1.18</v>
@@ -7699,13 +7699,13 @@
         <v>1.61</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CT17" t="n">
         <v>3.19</v>
@@ -7714,10 +7714,10 @@
         <v>1.62</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CX17" t="n">
         <v>1.53</v>
@@ -7735,52 +7735,52 @@
         <v>1.2</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="DH17" t="n">
-        <v>89.75</v>
+        <v>89.72</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="DM17" t="n">
-        <v>50.89</v>
+        <v>50.69</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.14</v>
+        <v>12.17</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.18</v>
+        <v>13.14</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.960000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DS17" t="n">
         <v>0.07000000000000001</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>48.11</v>
+        <v>48.45</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DX17" t="n">
         <v>13.93</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.359999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.86</v>
+        <v>20.69</v>
       </c>
       <c r="EB17" t="n">
         <v>1.57</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
+++ b/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
         <v>0.14</v>
@@ -1472,136 +1472,136 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.36</v>
+        <v>4.07</v>
       </c>
       <c r="AI2" t="n">
-        <v>96.20999999999999</v>
+        <v>96</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.86</v>
+        <v>6.67</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AN2" t="n">
-        <v>56.07</v>
+        <v>55.87</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.07</v>
+        <v>11.93</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>11.47</v>
       </c>
       <c r="AS2" t="n">
         <v>8.07</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>61.43</v>
+        <v>61.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BA2" t="n">
-        <v>14.5</v>
+        <v>14.07</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.5</v>
+        <v>9.27</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.57</v>
+        <v>20.67</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="BH2" t="n">
-        <v>11.29</v>
+        <v>11.07</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.71</v>
+        <v>5.55</v>
       </c>
       <c r="BR2" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS2" t="n">
-        <v>89.29000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="BT2" t="n">
-        <v>75</v>
+        <v>75.86</v>
       </c>
       <c r="BU2" t="n">
-        <v>39.29</v>
+        <v>41.38</v>
       </c>
       <c r="BV2" t="n">
-        <v>25</v>
+        <v>24.14</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BX2" t="n">
-        <v>64.29000000000001</v>
+        <v>62.07</v>
       </c>
       <c r="BY2" t="n">
         <v>1.77</v>
@@ -1610,16 +1610,16 @@
         <v>1.86</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="CE2" t="n">
         <v>1.27</v>
@@ -1634,7 +1634,7 @@
         <v>1.6</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.59</v>
@@ -1646,10 +1646,10 @@
         <v>1.6</v>
       </c>
       <c r="CM2" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CO2" t="n">
         <v>1.17</v>
@@ -1673,10 +1673,10 @@
         <v>1.59</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX2" t="n">
         <v>1.51</v>
@@ -1688,7 +1688,7 @@
         <v>2.46</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DB2" t="n">
         <v>1.2</v>
@@ -1700,79 +1700,79 @@
         <v>2.56</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.86</v>
+        <v>3.73</v>
       </c>
       <c r="DH2" t="n">
-        <v>104</v>
+        <v>103.62</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="DK2" t="n">
-        <v>7.18</v>
+        <v>7.07</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="DM2" t="n">
-        <v>61.5</v>
+        <v>61.21</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.18</v>
+        <v>12.1</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.93</v>
+        <v>11.9</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.72</v>
+        <v>6.76</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>61.75</v>
+        <v>61.62</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.28</v>
+        <v>15.04</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.779999999999999</v>
+        <v>9.66</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.89</v>
+        <v>24.79</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="F3" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="G3" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="H3" t="n">
-        <v>95.29000000000001</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0.29</v>
+        <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>43.36</v>
+        <v>45.13</v>
       </c>
       <c r="N3" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="O3" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="P3" t="n">
-        <v>13.36</v>
+        <v>13.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.57</v>
+        <v>10.47</v>
       </c>
       <c r="R3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="V3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>48.57</v>
+        <v>49.27</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.64</v>
+        <v>12.93</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.64</v>
+        <v>8</v>
       </c>
       <c r="AB3" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>25.79</v>
+        <v>26.07</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>0.14</v>
@@ -1953,70 +1953,70 @@
         <v>1.57</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="BH3" t="n">
-        <v>10</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>96.55</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>82.76000000000001</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="CB3" t="n">
         <v>4.29</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>96.43000000000001</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>82.14</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>53.57</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>39.29</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>21.43</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>4.3</v>
       </c>
       <c r="CC3" t="n">
         <v>6.25</v>
@@ -2031,16 +2031,16 @@
         <v>2.54</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CH3" t="n">
         <v>1.49</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK3" t="n">
         <v>1.35</v>
@@ -2049,7 +2049,7 @@
         <v>1.69</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CN3" t="n">
         <v>2.23</v>
@@ -2058,16 +2058,16 @@
         <v>1.24</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CR3" t="n">
         <v>1.4</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CT3" t="n">
         <v>3.09</v>
@@ -2076,106 +2076,106 @@
         <v>1.51</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX3" t="n">
         <v>1.5</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.48</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DB3" t="n">
         <v>1.27</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="DH3" t="n">
-        <v>89.25</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM3" t="n">
-        <v>37.46</v>
+        <v>38.58</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.61</v>
+        <v>12.59</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.64</v>
+        <v>10.59</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.82</v>
+        <v>9.59</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.96</v>
+        <v>44.49</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.86</v>
+        <v>11.07</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.89</v>
+        <v>7.1</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="EA3" t="n">
-        <v>21.79</v>
+        <v>22.07</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="4">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>0.57</v>
+        <v>0.87</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="H5" t="n">
-        <v>95.56999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.93</v>
+        <v>1.27</v>
       </c>
       <c r="K5" t="n">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
       <c r="L5" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="M5" t="n">
-        <v>50.36</v>
+        <v>49.27</v>
       </c>
       <c r="N5" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="O5" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="P5" t="n">
-        <v>10.57</v>
+        <v>10.53</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.859999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="R5" t="n">
-        <v>9.859999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="S5" t="n">
         <v>1.07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="V5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>46.57</v>
+        <v>46.4</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.43</v>
+        <v>12.4</v>
       </c>
       <c r="AA5" t="n">
         <v>8.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.93</v>
+        <v>21.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.93</v>
+        <v>1.27</v>
       </c>
       <c r="AF5" t="n">
         <v>0.07000000000000001</v>
@@ -2759,70 +2759,70 @@
         <v>1.64</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.14</v>
+        <v>10.07</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.43</v>
+        <v>4.45</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.25</v>
+        <v>5.17</v>
       </c>
       <c r="BR5" t="n">
-        <v>89.29000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="BS5" t="n">
-        <v>67.86</v>
+        <v>65.52</v>
       </c>
       <c r="BT5" t="n">
-        <v>39.29</v>
+        <v>37.93</v>
       </c>
       <c r="BU5" t="n">
-        <v>21.43</v>
+        <v>20.69</v>
       </c>
       <c r="BV5" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BX5" t="n">
-        <v>46.43</v>
+        <v>44.83</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="CC5" t="n">
         <v>3.65</v>
@@ -2831,43 +2831,43 @@
         <v>3.92</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CH5" t="n">
         <v>1.43</v>
       </c>
       <c r="CI5" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CR5" t="n">
         <v>1.43</v>
@@ -2885,70 +2885,70 @@
         <v>2.1</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX5" t="n">
         <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.38</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DB5" t="n">
         <v>1.3</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="DE5" t="n">
         <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="DH5" t="n">
-        <v>95.72</v>
+        <v>95.73</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.61</v>
+        <v>45.21</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.36</v>
+        <v>10.34</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.36</v>
+        <v>10.45</v>
       </c>
       <c r="DR5" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="DS5" t="n">
         <v>0.14</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.72</v>
+        <v>46.62</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.61</v>
+        <v>11.62</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.29</v>
+        <v>7.31</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.25</v>
+        <v>21.38</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="F6" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="G6" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>86</v>
+        <v>86.47</v>
       </c>
       <c r="I6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="K6" t="n">
-        <v>4.86</v>
+        <v>5.27</v>
       </c>
       <c r="L6" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>43.79</v>
+        <v>45.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="O6" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="P6" t="n">
-        <v>11.93</v>
+        <v>12.07</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.07</v>
+        <v>10.8</v>
       </c>
       <c r="R6" t="n">
-        <v>8.57</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="T6" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="V6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>41.86</v>
+        <v>42.73</v>
       </c>
       <c r="Y6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.29</v>
+        <v>13.07</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.93</v>
+        <v>7.33</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.36</v>
+        <v>5.73</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.14</v>
+        <v>18.47</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF6" t="n">
         <v>0.07000000000000001</v>
@@ -3162,70 +3162,70 @@
         <v>1.57</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.79</v>
+        <v>10.97</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.14</v>
+        <v>4.21</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.71</v>
+        <v>5.86</v>
       </c>
       <c r="BR6" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS6" t="n">
-        <v>85.70999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>60.71</v>
+        <v>62.07</v>
       </c>
       <c r="BU6" t="n">
-        <v>32.14</v>
+        <v>34.48</v>
       </c>
       <c r="BV6" t="n">
-        <v>3.57</v>
+        <v>6.9</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="BX6" t="n">
-        <v>57.14</v>
+        <v>55.17</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.32</v>
+        <v>3.19</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="CC6" t="n">
         <v>5.22</v>
@@ -3234,16 +3234,16 @@
         <v>6.47</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI6" t="n">
         <v>2.09</v>
@@ -3270,7 +3270,7 @@
         <v>1.74</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
@@ -3300,91 +3300,91 @@
         <v>2.49</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DB6" t="n">
         <v>1.24</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="DH6" t="n">
-        <v>82.93000000000001</v>
+        <v>83.28</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.61</v>
+        <v>4.83</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="DM6" t="n">
-        <v>39.39</v>
+        <v>40.28</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.64</v>
+        <v>11.73</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.78</v>
+        <v>10.66</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.07</v>
+        <v>9</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>41.93</v>
+        <v>42.38</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.9</v>
+        <v>12.31</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.43</v>
+        <v>7.62</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.47</v>
+        <v>4.69</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.92</v>
+        <v>19.07</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="n">
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,52 +3484,52 @@
         <v>1.43</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AI7" t="n">
-        <v>74.5</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AN7" t="n">
-        <v>30.07</v>
+        <v>30.33</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.71</v>
+        <v>11.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.21</v>
+        <v>11.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>10.93</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AV7" t="n">
         <v>0.07000000000000001</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>42.79</v>
+        <v>42.93</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.57</v>
+        <v>8.67</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.93</v>
+        <v>5.13</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.64</v>
+        <v>3.53</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.71</v>
+        <v>18.07</v>
       </c>
       <c r="BE7" t="n">
         <v>1.02</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.29</v>
+        <v>3.34</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.93</v>
+        <v>11.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.29</v>
+        <v>3.34</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.21</v>
+        <v>5.38</v>
       </c>
       <c r="BR7" t="n">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>85.70999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>64.29000000000001</v>
+        <v>65.52</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>51.72</v>
       </c>
       <c r="BV7" t="n">
-        <v>32.14</v>
+        <v>34.48</v>
       </c>
       <c r="BW7" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="BX7" t="n">
-        <v>42.86</v>
+        <v>41.38</v>
       </c>
       <c r="BY7" t="n">
         <v>5.99</v>
@@ -3625,22 +3625,22 @@
         <v>6.49</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.57</v>
+        <v>5.54</v>
       </c>
       <c r="CB7" t="n">
-        <v>6.15</v>
+        <v>6.12</v>
       </c>
       <c r="CC7" t="n">
-        <v>14.56</v>
+        <v>14.03</v>
       </c>
       <c r="CD7" t="n">
-        <v>12.57</v>
+        <v>12.24</v>
       </c>
       <c r="CE7" t="n">
         <v>1.25</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CG7" t="n">
         <v>3.69</v>
@@ -3649,10 +3649,10 @@
         <v>1.68</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK7" t="n">
         <v>1.31</v>
@@ -3664,7 +3664,7 @@
         <v>3.25</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CO7" t="n">
         <v>1.15</v>
@@ -3688,7 +3688,7 @@
         <v>1.7</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CW7" t="n">
         <v>1.84</v>
@@ -3703,7 +3703,7 @@
         <v>2.5</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DB7" t="n">
         <v>1.19</v>
@@ -3712,82 +3712,82 @@
         <v>1.57</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DE7" t="n">
         <v>0.1</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.78</v>
+        <v>80.86</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.29</v>
+        <v>33.31</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.46</v>
+        <v>11.31</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.71</v>
+        <v>11.79</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.9</v>
+        <v>10.86</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>44.04</v>
+        <v>44.07</v>
       </c>
       <c r="DW7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.779999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.28</v>
+        <v>5.38</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.36</v>
+        <v>19</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="8">
@@ -4362,7 +4362,7 @@
         <v>3.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.53</v>
+        <v>19.6</v>
       </c>
       <c r="BE9" t="n">
         <v>1.16</v>
@@ -4587,7 +4587,7 @@
         <v>3.86</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.62</v>
+        <v>19.65</v>
       </c>
       <c r="EB9" t="n">
         <v>1.25</v>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
         <v>14</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="G10" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="n">
-        <v>108.07</v>
+        <v>105.33</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="K10" t="n">
-        <v>7.21</v>
+        <v>6.8</v>
       </c>
       <c r="L10" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="M10" t="n">
-        <v>61.07</v>
+        <v>59.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="O10" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="P10" t="n">
-        <v>11.36</v>
+        <v>11.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>11</v>
+        <v>10.93</v>
       </c>
       <c r="R10" t="n">
-        <v>5.93</v>
+        <v>5.87</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T10" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="U10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.57</v>
+        <v>56.53</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.43</v>
+        <v>15.93</v>
       </c>
       <c r="AA10" t="n">
-        <v>11</v>
+        <v>10.53</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.43</v>
+        <v>5.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.71</v>
+        <v>18.47</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AF10" t="n">
         <v>0.14</v>
@@ -4774,70 +4774,70 @@
         <v>2.29</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.18</v>
+        <v>10</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.93</v>
+        <v>1.03</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="BP10" t="n">
         <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.89</v>
+        <v>4.76</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>75</v>
+        <v>75.86</v>
       </c>
       <c r="BT10" t="n">
-        <v>60.71</v>
+        <v>62.07</v>
       </c>
       <c r="BU10" t="n">
-        <v>35.71</v>
+        <v>37.93</v>
       </c>
       <c r="BV10" t="n">
-        <v>25</v>
+        <v>24.14</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>48.28</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="CC10" t="n">
         <v>3.03</v>
@@ -4849,10 +4849,10 @@
         <v>1.28</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CH10" t="n">
         <v>1.58</v>
@@ -4861,16 +4861,16 @@
         <v>2.22</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CL10" t="n">
         <v>1.73</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CN10" t="n">
         <v>2.16</v>
@@ -4897,7 +4897,7 @@
         <v>1.59</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CW10" t="n">
         <v>1.64</v>
@@ -4927,76 +4927,76 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="DH10" t="n">
-        <v>99.5</v>
+        <v>98.38</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.75</v>
+        <v>5.59</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="DM10" t="n">
-        <v>53.68</v>
+        <v>52.97</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.96</v>
+        <v>10.93</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.36</v>
+        <v>7.28</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.96</v>
+        <v>54.52</v>
       </c>
       <c r="DW10" t="n">
         <v>0.1</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.78</v>
+        <v>13.62</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.32</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.75</v>
+        <v>19.59</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="11">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
         <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>0.14</v>
@@ -5499,52 +5499,52 @@
         <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
-        <v>101.64</v>
+        <v>98.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AL12" t="n">
-        <v>5.29</v>
+        <v>5.4</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AN12" t="n">
-        <v>45.71</v>
+        <v>45.87</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.29</v>
+        <v>13.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.36</v>
+        <v>13.27</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.93</v>
+        <v>8.73</v>
       </c>
       <c r="AT12" t="n">
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="AV12" t="n">
         <v>0.07000000000000001</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>54.71</v>
+        <v>54.13</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BA12" t="n">
-        <v>14.93</v>
+        <v>15.53</v>
       </c>
       <c r="BB12" t="n">
-        <v>10.14</v>
+        <v>10.07</v>
       </c>
       <c r="BC12" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BP12" t="n">
         <v>4.79</v>
       </c>
-      <c r="BD12" t="n">
-        <v>20.93</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>4.71</v>
-      </c>
       <c r="BQ12" t="n">
-        <v>5.5</v>
+        <v>5.66</v>
       </c>
       <c r="BR12" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS12" t="n">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>67.86</v>
+        <v>68.97</v>
       </c>
       <c r="BU12" t="n">
-        <v>42.86</v>
+        <v>44.83</v>
       </c>
       <c r="BV12" t="n">
-        <v>17.86</v>
+        <v>20.69</v>
       </c>
       <c r="BW12" t="n">
-        <v>3.57</v>
+        <v>6.9</v>
       </c>
       <c r="BX12" t="n">
-        <v>57.14</v>
+        <v>58.62</v>
       </c>
       <c r="BY12" t="n">
         <v>2.44</v>
@@ -5640,16 +5640,16 @@
         <v>2.55</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.55</v>
+        <v>3.46</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.77</v>
+        <v>3.68</v>
       </c>
       <c r="CE12" t="n">
         <v>1.27</v>
@@ -5658,28 +5658,28 @@
         <v>2.27</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CH12" t="n">
         <v>1.61</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CM12" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CO12" t="n">
         <v>1.17</v>
@@ -5688,7 +5688,7 @@
         <v>1.57</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CR12" t="n">
         <v>1.37</v>
@@ -5703,10 +5703,10 @@
         <v>1.62</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CX12" t="n">
         <v>1.51</v>
@@ -5724,52 +5724,52 @@
         <v>1.18</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="DH12" t="n">
-        <v>98.28</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.36</v>
+        <v>4.45</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.96</v>
+        <v>43.14</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.04</v>
+        <v>13.21</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.75</v>
+        <v>12.72</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.96</v>
+        <v>7.89</v>
       </c>
       <c r="DS12" t="n">
         <v>0.04</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>53.71</v>
+        <v>53.44</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>14</v>
+        <v>14.34</v>
       </c>
       <c r="DY12" t="n">
         <v>9.039999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.96</v>
+        <v>5.31</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.72</v>
+        <v>18.62</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
         <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>0.14</v>
@@ -5902,139 +5902,139 @@
         <v>1.36</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.64</v>
+        <v>3.33</v>
       </c>
       <c r="AI13" t="n">
-        <v>98.14</v>
+        <v>96.2</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.86</v>
+        <v>5.53</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="AN13" t="n">
-        <v>55.79</v>
+        <v>54.73</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.57</v>
+        <v>11.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.21</v>
+        <v>10.33</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.289999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>49.64</v>
+        <v>49.07</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA13" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.93</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.57</v>
+        <v>5.73</v>
       </c>
       <c r="BD13" t="n">
-        <v>19.14</v>
+        <v>18.73</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="BH13" t="n">
-        <v>11.89</v>
+        <v>11.69</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="BN13" t="n">
         <v>1.93</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.46</v>
+        <v>5.24</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.43</v>
+        <v>6.17</v>
       </c>
       <c r="BR13" t="n">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>85.70999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>67.86</v>
+        <v>68.97</v>
       </c>
       <c r="BU13" t="n">
-        <v>53.57</v>
+        <v>51.72</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>24.14</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BX13" t="n">
-        <v>67.86</v>
+        <v>65.52</v>
       </c>
       <c r="BY13" t="n">
         <v>2.46</v>
@@ -6043,25 +6043,25 @@
         <v>2.56</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.05</v>
+        <v>4.02</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="CC13" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="CD13" t="n">
         <v>4.16</v>
-      </c>
-      <c r="CD13" t="n">
-        <v>4.24</v>
       </c>
       <c r="CE13" t="n">
         <v>1.26</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CH13" t="n">
         <v>1.62</v>
@@ -6088,10 +6088,10 @@
         <v>1.15</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CR13" t="n">
         <v>1.38</v>
@@ -6103,7 +6103,7 @@
         <v>3.15</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CV13" t="n">
         <v>2.6</v>
@@ -6133,79 +6133,79 @@
         <v>2.41</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.39</v>
+        <v>3.24</v>
       </c>
       <c r="DH13" t="n">
-        <v>95.78</v>
+        <v>94.86</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.93</v>
+        <v>5.76</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="DM13" t="n">
-        <v>54.61</v>
+        <v>54.1</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.68</v>
+        <v>11.59</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.25</v>
+        <v>11.28</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.75</v>
+        <v>7.86</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.07</v>
+        <v>48.79</v>
       </c>
       <c r="DW13" t="n">
         <v>0.04</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.4</v>
+        <v>14.28</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.359999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.18</v>
+        <v>19.93</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="14">
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
         <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="H14" t="n">
-        <v>91.64</v>
+        <v>90.87</v>
       </c>
       <c r="I14" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K14" t="n">
-        <v>5.71</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="M14" t="n">
-        <v>46.07</v>
+        <v>46.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="O14" t="n">
-        <v>2.64</v>
+        <v>2.87</v>
       </c>
       <c r="P14" t="n">
-        <v>10.71</v>
+        <v>10.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.140000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="R14" t="n">
         <v>9.93</v>
       </c>
       <c r="S14" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>46.57</v>
+        <v>47.07</v>
       </c>
       <c r="Y14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>14</v>
+        <v>14.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.210000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.79</v>
+        <v>4.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>16.64</v>
+        <v>16.47</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6386,70 +6386,70 @@
         <v>1.14</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="BH14" t="n">
-        <v>12.82</v>
+        <v>12.97</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="BP14" t="n">
-        <v>6.07</v>
+        <v>6.1</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.18</v>
+        <v>6.31</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>78.56999999999999</v>
+        <v>79.31</v>
       </c>
       <c r="BU14" t="n">
-        <v>39.29</v>
+        <v>41.38</v>
       </c>
       <c r="BV14" t="n">
-        <v>28.57</v>
+        <v>31.03</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BX14" t="n">
-        <v>64.29000000000001</v>
+        <v>65.52</v>
       </c>
       <c r="BY14" t="n">
         <v>3.05</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.61</v>
+        <v>4.59</v>
       </c>
       <c r="CC14" t="n">
         <v>5.55</v>
@@ -6464,16 +6464,16 @@
         <v>2.27</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CH14" t="n">
         <v>1.64</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK14" t="n">
         <v>1.26</v>
@@ -6488,13 +6488,13 @@
         <v>2.55</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP14" t="n">
         <v>1.55</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CR14" t="n">
         <v>1.36</v>
@@ -6509,10 +6509,10 @@
         <v>1.67</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
@@ -6523,88 +6523,88 @@
         <v>2.39</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DE14" t="n">
         <v>0.1</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="DH14" t="n">
-        <v>87.31999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.64</v>
+        <v>5.79</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="DM14" t="n">
-        <v>41.75</v>
+        <v>42.07</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.21</v>
+        <v>10.27</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.11</v>
+        <v>10.35</v>
       </c>
       <c r="DR14" t="n">
-        <v>10.64</v>
+        <v>10.62</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>45.32</v>
+        <v>45.62</v>
       </c>
       <c r="DW14" t="n">
         <v>0.04</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.28</v>
+        <v>12.51</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.1</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.18</v>
+        <v>4.24</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.1</v>
+        <v>17.97</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="15">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>0.21</v>
@@ -7107,139 +7107,139 @@
         <v>1.21</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AI16" t="n">
-        <v>89.29000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AJ16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AL16" t="n">
-        <v>6.43</v>
+        <v>6.33</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AN16" t="n">
-        <v>46.07</v>
+        <v>47.27</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="AQ16" t="n">
         <v>13.07</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.64</v>
+        <v>11.53</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.36</v>
+        <v>7.53</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA16" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.57</v>
+        <v>7.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.43</v>
+        <v>5.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>24</v>
+        <v>23.87</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.79</v>
+        <v>3.69</v>
       </c>
       <c r="BH16" t="n">
-        <v>12.21</v>
+        <v>12.07</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.79</v>
+        <v>3.69</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN16" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="BP16" t="n">
-        <v>6.68</v>
+        <v>6.62</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="BR16" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS16" t="n">
-        <v>82.14</v>
+        <v>79.31</v>
       </c>
       <c r="BT16" t="n">
-        <v>78.56999999999999</v>
+        <v>75.86</v>
       </c>
       <c r="BU16" t="n">
-        <v>57.14</v>
+        <v>55.17</v>
       </c>
       <c r="BV16" t="n">
-        <v>28.57</v>
+        <v>27.59</v>
       </c>
       <c r="BW16" t="n">
-        <v>25</v>
+        <v>24.14</v>
       </c>
       <c r="BX16" t="n">
-        <v>71.43000000000001</v>
+        <v>68.97</v>
       </c>
       <c r="BY16" t="n">
         <v>1.66</v>
@@ -7248,16 +7248,16 @@
         <v>1.71</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.62</v>
+        <v>4.63</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="CE16" t="n">
         <v>1.24</v>
@@ -7266,16 +7266,16 @@
         <v>2.18</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CH16" t="n">
         <v>1.67</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CK16" t="n">
         <v>1.26</v>
@@ -7284,10 +7284,10 @@
         <v>1.51</v>
       </c>
       <c r="CM16" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CO16" t="n">
         <v>1.13</v>
@@ -7311,22 +7311,22 @@
         <v>1.71</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX16" t="n">
         <v>1.5</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.45</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DB16" t="n">
         <v>1.16</v>
@@ -7338,79 +7338,79 @@
         <v>2.3</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="DG16" t="n">
         <v>2.93</v>
       </c>
       <c r="DH16" t="n">
-        <v>95.54000000000001</v>
+        <v>96.52</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="DK16" t="n">
-        <v>7.9</v>
+        <v>7.79</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DM16" t="n">
-        <v>55.96</v>
+        <v>56.24</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DO16" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.32</v>
+        <v>12.35</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.5</v>
+        <v>11.45</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.68</v>
+        <v>6.79</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>50.72</v>
+        <v>50.9</v>
       </c>
       <c r="DW16" t="n">
         <v>0.04</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.75</v>
+        <v>15.76</v>
       </c>
       <c r="DY16" t="n">
-        <v>10.07</v>
+        <v>10</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.68</v>
+        <v>5.76</v>
       </c>
       <c r="EA16" t="n">
-        <v>23.04</v>
+        <v>23</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="17">
@@ -7468,7 +7468,7 @@
         <v>12.93</v>
       </c>
       <c r="R17" t="n">
-        <v>8.4</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="S17" t="n">
         <v>1.4</v>
@@ -7492,10 +7492,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>16.87</v>
+        <v>16.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>11</v>
+        <v>10.93</v>
       </c>
       <c r="AB17" t="n">
         <v>5.87</v>
@@ -7780,7 +7780,7 @@
         <v>13.14</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.859999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="DS17" t="n">
         <v>0.07000000000000001</v>
@@ -7798,10 +7798,10 @@
         <v>0.14</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.93</v>
+        <v>13.9</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.34</v>
+        <v>9.31</v>
       </c>
       <c r="DZ17" t="n">
         <v>4.59</v>

--- a/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
+++ b/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
@@ -1824,13 +1824,13 @@
         <v>1.6</v>
       </c>
       <c r="P3" t="n">
-        <v>13.27</v>
+        <v>13.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.47</v>
+        <v>10.4</v>
       </c>
       <c r="R3" t="n">
-        <v>8.27</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>1.6</v>
@@ -1848,22 +1848,22 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>49.27</v>
+        <v>49.2</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.93</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>8</v>
+        <v>8.07</v>
       </c>
       <c r="AB3" t="n">
         <v>4.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.07</v>
+        <v>26.2</v>
       </c>
       <c r="AD3" t="n">
         <v>1.39</v>
@@ -1956,7 +1956,7 @@
         <v>3.03</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.859999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="BI3" t="n">
         <v>3.03</v>
@@ -2136,13 +2136,13 @@
         <v>1.31</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.59</v>
+        <v>12.55</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.59</v>
+        <v>10.55</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.59</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DS3" t="n">
         <v>0.1</v>
@@ -2154,22 +2154,22 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.49</v>
+        <v>44.45</v>
       </c>
       <c r="DW3" t="n">
         <v>0.03</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.07</v>
+        <v>11.1</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.1</v>
+        <v>7.14</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.96</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.07</v>
+        <v>22.14</v>
       </c>
       <c r="EB3" t="n">
         <v>1.21</v>
@@ -2293,7 +2293,7 @@
         <v>1.13</v>
       </c>
       <c r="AL4" t="n">
-        <v>7.73</v>
+        <v>7.47</v>
       </c>
       <c r="AM4" t="n">
         <v>0.87</v>
@@ -2308,13 +2308,13 @@
         <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.73</v>
+        <v>8.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.6</v>
+        <v>11.53</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>7.07</v>
       </c>
       <c r="AT4" t="n">
         <v>1.13</v>
@@ -2332,22 +2332,22 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>62.8</v>
+        <v>61.87</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA4" t="n">
-        <v>16.4</v>
+        <v>16.67</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.53</v>
+        <v>10.87</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.87</v>
+        <v>5.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.33</v>
+        <v>18.8</v>
       </c>
       <c r="BE4" t="n">
         <v>1.83</v>
@@ -2359,7 +2359,7 @@
         <v>3.72</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.97</v>
+        <v>10.83</v>
       </c>
       <c r="BI4" t="n">
         <v>3.72</v>
@@ -2524,7 +2524,7 @@
         <v>0.83</v>
       </c>
       <c r="DK4" t="n">
-        <v>7.89</v>
+        <v>7.76</v>
       </c>
       <c r="DL4" t="n">
         <v>0.79</v>
@@ -2539,13 +2539,13 @@
         <v>4</v>
       </c>
       <c r="DP4" t="n">
-        <v>8.52</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.93</v>
+        <v>10.41</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.48</v>
+        <v>5.62</v>
       </c>
       <c r="DS4" t="n">
         <v>0.17</v>
@@ -2557,22 +2557,22 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>63.83</v>
+        <v>63.35</v>
       </c>
       <c r="DW4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX4" t="n">
-        <v>18.07</v>
+        <v>18.21</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.72</v>
+        <v>11.9</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.35</v>
+        <v>6.31</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.65</v>
+        <v>18.9</v>
       </c>
       <c r="EB4" t="n">
         <v>2.05</v>
@@ -3842,10 +3842,10 @@
         <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.93</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>6.53</v>
       </c>
       <c r="S8" t="n">
         <v>1.47</v>
@@ -3863,22 +3863,22 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>49.73</v>
+        <v>50.67</v>
       </c>
       <c r="Y8" t="n">
         <v>0.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.6</v>
+        <v>12.73</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.73</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="AB8" t="n">
         <v>3.87</v>
       </c>
       <c r="AC8" t="n">
-        <v>16.47</v>
+        <v>16.93</v>
       </c>
       <c r="AD8" t="n">
         <v>1.43</v>
@@ -3971,7 +3971,7 @@
         <v>2.79</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.9</v>
+        <v>8.76</v>
       </c>
       <c r="BI8" t="n">
         <v>2.79</v>
@@ -4154,10 +4154,10 @@
         <v>11.52</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.07</v>
+        <v>10.35</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.38</v>
+        <v>6.66</v>
       </c>
       <c r="DS8" t="n">
         <v>0.07000000000000001</v>
@@ -4169,22 +4169,22 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.55</v>
+        <v>50.04</v>
       </c>
       <c r="DW8" t="n">
         <v>0.1</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.28</v>
+        <v>11.34</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.45</v>
+        <v>7.52</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.83</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.48</v>
+        <v>17.72</v>
       </c>
       <c r="EB8" t="n">
         <v>1.3</v>
@@ -5920,7 +5920,7 @@
         <v>1.73</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.53</v>
+        <v>5.6</v>
       </c>
       <c r="AM13" t="n">
         <v>0.13</v>
@@ -5935,10 +5935,10 @@
         <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.4</v>
+        <v>11.33</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.33</v>
+        <v>10.27</v>
       </c>
       <c r="AS13" t="n">
         <v>8.470000000000001</v>
@@ -5959,25 +5959,25 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>49.07</v>
+        <v>49.13</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA13" t="n">
-        <v>15.2</v>
+        <v>15.53</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.470000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.73</v>
+        <v>5.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.73</v>
+        <v>18.87</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BF13" t="n">
         <v>1.6</v>
@@ -5986,7 +5986,7 @@
         <v>3.34</v>
       </c>
       <c r="BH13" t="n">
-        <v>11.69</v>
+        <v>11.72</v>
       </c>
       <c r="BI13" t="n">
         <v>3.34</v>
@@ -6151,7 +6151,7 @@
         <v>1.55</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.76</v>
+        <v>5.79</v>
       </c>
       <c r="DL13" t="n">
         <v>0.34</v>
@@ -6166,10 +6166,10 @@
         <v>2.42</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.59</v>
+        <v>11.55</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.28</v>
+        <v>11.25</v>
       </c>
       <c r="DR13" t="n">
         <v>7.86</v>
@@ -6184,25 +6184,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.79</v>
+        <v>48.83</v>
       </c>
       <c r="DW13" t="n">
         <v>0.04</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.28</v>
+        <v>14.45</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.140000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.93</v>
+        <v>20</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="EC13" t="n">
         <v>1.48</v>

--- a/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
+++ b/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="H2" t="n">
-        <v>111.79</v>
+        <v>112.8</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="K2" t="n">
-        <v>7.5</v>
+        <v>7.53</v>
       </c>
       <c r="L2" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>66.93000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="O2" t="n">
-        <v>2.79</v>
+        <v>2.93</v>
       </c>
       <c r="P2" t="n">
-        <v>12.29</v>
+        <v>12.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.36</v>
+        <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>5.36</v>
+        <v>5.27</v>
       </c>
       <c r="S2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="U2" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>62.07</v>
+        <v>62.8</v>
       </c>
       <c r="Y2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.07</v>
+        <v>16.27</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.07</v>
+        <v>10.13</v>
       </c>
       <c r="AB2" t="n">
-        <v>6</v>
+        <v>6.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.21</v>
+        <v>28.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AF2" t="n">
         <v>0.07000000000000001</v>
@@ -1550,70 +1550,70 @@
         <v>1.73</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="BH2" t="n">
         <v>11.07</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.55</v>
+        <v>4.67</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.55</v>
+        <v>5.47</v>
       </c>
       <c r="BR2" t="n">
-        <v>96.55</v>
+        <v>96.67</v>
       </c>
       <c r="BS2" t="n">
-        <v>89.66</v>
+        <v>90</v>
       </c>
       <c r="BT2" t="n">
-        <v>75.86</v>
+        <v>76.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>41.38</v>
+        <v>43.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>24.14</v>
+        <v>23.33</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="BX2" t="n">
-        <v>62.07</v>
+        <v>63.33</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.19</v>
+        <v>4.25</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.41</v>
+        <v>4.48</v>
       </c>
       <c r="CC2" t="n">
         <v>2.45</v>
@@ -1625,13 +1625,13 @@
         <v>1.27</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CI2" t="n">
         <v>2.3</v>
@@ -1640,37 +1640,37 @@
         <v>1.59</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CL2" t="n">
         <v>1.6</v>
       </c>
       <c r="CM2" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CO2" t="n">
         <v>1.17</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CT2" t="n">
         <v>3.18</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CV2" t="n">
         <v>2.36</v>
@@ -1682,97 +1682,97 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.46</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DB2" t="n">
         <v>1.2</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="DE2" t="n">
         <v>0.1</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="DH2" t="n">
-        <v>103.62</v>
+        <v>104.4</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="DK2" t="n">
-        <v>7.07</v>
+        <v>7.1</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="DM2" t="n">
-        <v>61.21</v>
+        <v>62.34</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.1</v>
+        <v>12.06</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.9</v>
+        <v>11.74</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.76</v>
+        <v>6.67</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>61.62</v>
+        <v>62</v>
       </c>
       <c r="DW2" t="n">
         <v>0.1</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.04</v>
+        <v>15.17</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.66</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.38</v>
+        <v>5.46</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.79</v>
+        <v>24.74</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
         <v>0.27</v>
@@ -1872,52 +1872,52 @@
         <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AI3" t="n">
-        <v>83.20999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.79</v>
+        <v>3.13</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.57</v>
+        <v>32.33</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.86</v>
+        <v>11.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.71</v>
+        <v>10.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>10.53</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.86</v>
+        <v>1.07</v>
       </c>
       <c r="AV3" t="n">
         <v>0.07000000000000001</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>39.36</v>
+        <v>40.07</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.07</v>
+        <v>9.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.14</v>
+        <v>6.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.79</v>
+        <v>17.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="BH3" t="n">
         <v>9.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.1</v>
+        <v>4.13</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.28</v>
+        <v>4.3</v>
       </c>
       <c r="BR3" t="n">
-        <v>96.55</v>
+        <v>96.67</v>
       </c>
       <c r="BS3" t="n">
-        <v>82.76000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>55.17</v>
+        <v>56.67</v>
       </c>
       <c r="BU3" t="n">
-        <v>37.93</v>
+        <v>40</v>
       </c>
       <c r="BV3" t="n">
-        <v>20.69</v>
+        <v>23.33</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="BX3" t="n">
-        <v>55.17</v>
+        <v>56.67</v>
       </c>
       <c r="BY3" t="n">
         <v>2.93</v>
@@ -2013,31 +2013,31 @@
         <v>3.13</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="CC3" t="n">
-        <v>6.25</v>
+        <v>5.96</v>
       </c>
       <c r="CD3" t="n">
-        <v>7.08</v>
+        <v>6.75</v>
       </c>
       <c r="CE3" t="n">
         <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.73</v>
@@ -2046,40 +2046,40 @@
         <v>1.35</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CN3" t="n">
         <v>2.23</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP3" t="n">
         <v>1.78</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CU3" t="n">
         <v>1.51</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX3" t="n">
         <v>1.5</v>
@@ -2094,55 +2094,55 @@
         <v>2.15</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.90000000000001</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.83</v>
+        <v>3.96</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="DM3" t="n">
-        <v>38.58</v>
+        <v>38.73</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.55</v>
+        <v>12.4</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.55</v>
+        <v>10.4</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.720000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DS3" t="n">
         <v>0.1</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.45</v>
+        <v>44.64</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="DY3" t="n">
         <v>7.14</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.96</v>
+        <v>4.06</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.14</v>
+        <v>21.9</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="H4" t="n">
-        <v>109.36</v>
+        <v>110.07</v>
       </c>
       <c r="I4" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="K4" t="n">
-        <v>8.07</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>87.70999999999999</v>
+        <v>87.53</v>
       </c>
       <c r="N4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="O4" t="n">
-        <v>3.79</v>
+        <v>3.87</v>
       </c>
       <c r="P4" t="n">
-        <v>8.289999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.210000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="R4" t="n">
         <v>4.07</v>
       </c>
       <c r="S4" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="T4" t="n">
-        <v>3.21</v>
+        <v>3.33</v>
       </c>
       <c r="U4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>64.93000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="Y4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.86</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
         <v>13</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="AC4" t="n">
-        <v>19</v>
+        <v>18.93</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AF4" t="n">
         <v>0.47</v>
@@ -2356,70 +2356,70 @@
         <v>1.07</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.72</v>
+        <v>3.77</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.83</v>
+        <v>10.87</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.72</v>
+        <v>3.77</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="BN4" t="n">
         <v>2.03</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.48</v>
+        <v>5.53</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>89.66</v>
+        <v>90</v>
       </c>
       <c r="BT4" t="n">
-        <v>72.41</v>
+        <v>73.33</v>
       </c>
       <c r="BU4" t="n">
-        <v>44.83</v>
+        <v>46.67</v>
       </c>
       <c r="BV4" t="n">
-        <v>27.59</v>
+        <v>30</v>
       </c>
       <c r="BW4" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
       <c r="BX4" t="n">
-        <v>58.62</v>
+        <v>56.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.02</v>
+        <v>6.16</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.69</v>
+        <v>6.86</v>
       </c>
       <c r="CC4" t="n">
         <v>1.59</v>
@@ -2428,19 +2428,19 @@
         <v>1.6</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CF4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CG4" t="n">
-        <v>4.14</v>
+        <v>4.18</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.63</v>
@@ -2455,130 +2455,130 @@
         <v>3.19</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CO4" t="n">
         <v>1.09</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CT4" t="n">
         <v>3.32</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX4" t="n">
         <v>1.49</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.51</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DB4" t="n">
         <v>1.14</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="DH4" t="n">
-        <v>107.66</v>
+        <v>108.07</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DK4" t="n">
-        <v>7.76</v>
+        <v>7.74</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="DM4" t="n">
-        <v>76.62</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DO4" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="DP4" t="n">
-        <v>8.449999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10.41</v>
+        <v>10.23</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.62</v>
+        <v>5.57</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>63.35</v>
+        <v>63.23</v>
       </c>
       <c r="DW4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX4" t="n">
-        <v>18.21</v>
+        <v>18.33</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.9</v>
+        <v>11.93</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.31</v>
+        <v>6.4</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.9</v>
+        <v>18.87</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>0.2</v>
@@ -2681,49 +2681,49 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AI5" t="n">
-        <v>95.86</v>
+        <v>95</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>40.86</v>
+        <v>39.87</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.86</v>
+        <v>10.67</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.14</v>
+        <v>10.27</v>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="AU5" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>46.86</v>
+        <v>46.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.79</v>
+        <v>10.27</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.29</v>
+        <v>4.07</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.57</v>
+        <v>21.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.07</v>
+        <v>10.13</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.45</v>
+        <v>4.53</v>
       </c>
       <c r="BQ5" t="n">
         <v>5.17</v>
       </c>
       <c r="BR5" t="n">
-        <v>89.66</v>
+        <v>90</v>
       </c>
       <c r="BS5" t="n">
-        <v>65.52</v>
+        <v>66.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>37.93</v>
+        <v>40</v>
       </c>
       <c r="BU5" t="n">
-        <v>20.69</v>
+        <v>23.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>10.34</v>
+        <v>13.33</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="BX5" t="n">
-        <v>44.83</v>
+        <v>43.33</v>
       </c>
       <c r="BY5" t="n">
         <v>2.5</v>
@@ -2819,28 +2819,28 @@
         <v>2.65</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.61</v>
+        <v>3.82</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.77</v>
+        <v>4.04</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.65</v>
+        <v>4.64</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.92</v>
+        <v>5.19</v>
       </c>
       <c r="CE5" t="n">
         <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.95</v>
+        <v>3.03</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CI5" t="n">
         <v>2.01</v>
@@ -2852,103 +2852,103 @@
         <v>1.4</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="CR5" t="n">
         <v>1.43</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="CT5" t="n">
         <v>2.94</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="CV5" t="n">
         <v>2.1</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CX5" t="n">
         <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.38</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DB5" t="n">
         <v>1.3</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF5" t="n">
         <v>1.07</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="DH5" t="n">
-        <v>95.73</v>
+        <v>95.3</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.21</v>
+        <v>44.57</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.34</v>
+        <v>10.16</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.45</v>
+        <v>10.37</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.9</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="DS5" t="n">
         <v>0.14</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.62</v>
+        <v>46.4</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.62</v>
+        <v>11.34</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.31</v>
+        <v>7.14</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.31</v>
+        <v>4.2</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.38</v>
+        <v>21.4</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="n">
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>0.4</v>
@@ -3081,49 +3081,49 @@
         <v>1.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AG6" t="n">
         <v>1.07</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>79.86</v>
+        <v>79.33</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>35</v>
+        <v>33.67</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.36</v>
+        <v>11.13</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.5</v>
+        <v>10.53</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.57</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AU6" t="n">
         <v>1</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.93</v>
+        <v>7.47</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.71</v>
+        <v>20.13</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="BH6" t="n">
         <v>10.97</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BL6" t="n">
         <v>0.9</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.21</v>
+        <v>4.33</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.86</v>
+        <v>5.77</v>
       </c>
       <c r="BR6" t="n">
-        <v>96.55</v>
+        <v>96.67</v>
       </c>
       <c r="BS6" t="n">
-        <v>86.20999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>62.07</v>
+        <v>63.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>34.48</v>
+        <v>36.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="BX6" t="n">
-        <v>55.17</v>
+        <v>56.67</v>
       </c>
       <c r="BY6" t="n">
         <v>3.19</v>
@@ -3222,31 +3222,31 @@
         <v>3.35</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.28</v>
+        <v>4.36</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.22</v>
+        <v>5.47</v>
       </c>
       <c r="CD6" t="n">
-        <v>6.47</v>
+        <v>6.68</v>
       </c>
       <c r="CE6" t="n">
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.72</v>
@@ -3255,7 +3255,7 @@
         <v>1.28</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CM6" t="n">
         <v>3.3</v>
@@ -3264,94 +3264,94 @@
         <v>2.44</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="CT6" t="n">
         <v>3.14</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CV6" t="n">
         <v>2.19</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX6" t="n">
         <v>1.5</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.49</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="DH6" t="n">
-        <v>83.28</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>-0.03</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.83</v>
+        <v>4.77</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.28</v>
+        <v>39.43</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.73</v>
+        <v>11.6</v>
       </c>
       <c r="DQ6" t="n">
         <v>10.66</v>
       </c>
       <c r="DR6" t="n">
-        <v>9</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="DS6" t="n">
         <v>0.1</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42.38</v>
+        <v>41.86</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.31</v>
+        <v>12.04</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.69</v>
+        <v>4.63</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.07</v>
+        <v>19.3</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
         <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="G7" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="H7" t="n">
-        <v>87.06999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="K7" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="L7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>36.5</v>
+        <v>36.47</v>
       </c>
       <c r="N7" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>11.21</v>
+        <v>10.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.21</v>
+        <v>11.93</v>
       </c>
       <c r="R7" t="n">
-        <v>10.79</v>
+        <v>10.53</v>
       </c>
       <c r="S7" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="T7" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="U7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="V7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>45.29</v>
+        <v>45.6</v>
       </c>
       <c r="Y7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.64</v>
+        <v>5.53</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>20</v>
+        <v>19.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AF7" t="n">
         <v>0.2</v>
@@ -3565,70 +3565,70 @@
         <v>1.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.1</v>
+        <v>11.07</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="BL7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BM7" t="n">
         <v>0.93</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.9</v>
       </c>
       <c r="BN7" t="n">
         <v>1.83</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="BP7" t="n">
         <v>5.17</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.38</v>
+        <v>5.37</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.20999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>65.52</v>
+        <v>66.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>51.72</v>
+        <v>53.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>34.48</v>
+        <v>36.67</v>
       </c>
       <c r="BW7" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>41.38</v>
+        <v>43.33</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.99</v>
+        <v>5.83</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.49</v>
+        <v>6.29</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.54</v>
+        <v>5.48</v>
       </c>
       <c r="CB7" t="n">
-        <v>6.12</v>
+        <v>6.06</v>
       </c>
       <c r="CC7" t="n">
         <v>14.03</v>
@@ -3640,16 +3640,16 @@
         <v>1.25</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.76</v>
@@ -3658,13 +3658,13 @@
         <v>1.31</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CM7" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CO7" t="n">
         <v>1.15</v>
@@ -3673,25 +3673,25 @@
         <v>1.54</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS7" t="n">
         <v>2.33</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX7" t="n">
         <v>1.5</v>
@@ -3703,7 +3703,7 @@
         <v>2.5</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DB7" t="n">
         <v>1.19</v>
@@ -3712,49 +3712,49 @@
         <v>1.57</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.86</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.31</v>
+        <v>33.4</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.31</v>
+        <v>11.13</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.79</v>
+        <v>11.66</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.86</v>
+        <v>10.73</v>
       </c>
       <c r="DS7" t="n">
         <v>0.1</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>44.07</v>
+        <v>44.26</v>
       </c>
       <c r="DW7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.83</v>
+        <v>8.74</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.38</v>
+        <v>5.33</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="EA7" t="n">
-        <v>19</v>
+        <v>18.74</v>
       </c>
       <c r="EB7" t="n">
         <v>1.04</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
         <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
         <v>0.13</v>
@@ -3890,13 +3890,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="AI8" t="n">
-        <v>93.36</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="AJ8" t="n">
         <v>0.07000000000000001</v>
@@ -3905,121 +3905,121 @@
         <v>1.93</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.64</v>
+        <v>5.13</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AN8" t="n">
-        <v>37.21</v>
+        <v>38.47</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.29</v>
+        <v>11.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.79</v>
+        <v>6.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>49.36</v>
+        <v>50.13</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
         <v>6.07</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.79</v>
+        <v>3.93</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.57</v>
+        <v>19.47</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BF8" t="n">
         <v>1.93</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.76</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.9</v>
+        <v>5.03</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="BR8" t="n">
-        <v>89.66</v>
+        <v>90</v>
       </c>
       <c r="BS8" t="n">
-        <v>82.76000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>51.72</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>37.93</v>
+        <v>36.67</v>
       </c>
       <c r="BV8" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>62.07</v>
+        <v>60</v>
       </c>
       <c r="BY8" t="n">
         <v>2.44</v>
@@ -4028,166 +4028,166 @@
         <v>2.56</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CC8" t="n">
         <v>3.64</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CE8" t="n">
         <v>1.4</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CH8" t="n">
         <v>1.4</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK8" t="n">
         <v>1.52</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM8" t="n">
         <v>2.43</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CU8" t="n">
         <v>1.42</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX8" t="n">
         <v>1.6</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DA8" t="n">
         <v>1.84</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="DE8" t="n">
         <v>0.1</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="DH8" t="n">
-        <v>96</v>
+        <v>97.27</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.72</v>
+        <v>4.96</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.38</v>
+        <v>46.7</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.52</v>
+        <v>11.5</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.35</v>
+        <v>10.54</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.66</v>
+        <v>6.56</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.04</v>
+        <v>50.4</v>
       </c>
       <c r="DW8" t="n">
         <v>0.1</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.34</v>
+        <v>11.37</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.52</v>
+        <v>7.47</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.83</v>
+        <v>3.9</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.72</v>
+        <v>18.2</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC8" t="n">
         <v>1.93</v>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
         <v>15</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>92.20999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="I9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="K9" t="n">
-        <v>4.36</v>
+        <v>4.07</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>44.43</v>
+        <v>43.13</v>
       </c>
       <c r="N9" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="P9" t="n">
-        <v>9.859999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.43</v>
+        <v>10.67</v>
       </c>
       <c r="R9" t="n">
-        <v>10.07</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="U9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="V9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.79</v>
+        <v>45.47</v>
       </c>
       <c r="Y9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.71</v>
+        <v>11.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.57</v>
+        <v>7.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.71</v>
+        <v>19.47</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF9" t="n">
         <v>0.13</v>
@@ -4371,70 +4371,70 @@
         <v>1.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.38</v>
+        <v>10.17</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1.07</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.31</v>
+        <v>4.2</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.9</v>
+        <v>4.83</v>
       </c>
       <c r="BR9" t="n">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>79.31</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>58.62</v>
+        <v>60</v>
       </c>
       <c r="BU9" t="n">
-        <v>41.38</v>
+        <v>43.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>24.14</v>
+        <v>23.33</v>
       </c>
       <c r="BW9" t="n">
-        <v>13.79</v>
+        <v>13.33</v>
       </c>
       <c r="BX9" t="n">
-        <v>62.07</v>
+        <v>63.33</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.19</v>
+        <v>3.44</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.44</v>
+        <v>3.72</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.54</v>
+        <v>4.57</v>
       </c>
       <c r="CC9" t="n">
         <v>5.56</v>
@@ -4449,28 +4449,28 @@
         <v>2.3</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CH9" t="n">
         <v>1.6</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.62</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CM9" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CO9" t="n">
         <v>1.16</v>
@@ -4488,28 +4488,28 @@
         <v>2.45</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CU9" t="n">
         <v>1.62</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="DB9" t="n">
         <v>1.2</v>
@@ -4521,79 +4521,79 @@
         <v>2.53</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF9" t="n">
         <v>1.27</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="DH9" t="n">
-        <v>85</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="DI9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.31</v>
+        <v>4.17</v>
       </c>
       <c r="DL9" t="n">
         <v>0.24</v>
       </c>
       <c r="DM9" t="n">
-        <v>38.9</v>
+        <v>38.43</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="DP9" t="n">
-        <v>9.73</v>
+        <v>9.84</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.48</v>
+        <v>10.6</v>
       </c>
       <c r="DR9" t="n">
-        <v>10.45</v>
+        <v>10.34</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43</v>
+        <v>42.93</v>
       </c>
       <c r="DW9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.03</v>
+        <v>10.8</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.17</v>
+        <v>7</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.65</v>
+        <v>19.54</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
         <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,52 +4693,52 @@
         <v>2.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AP10" t="n">
         <v>1.93</v>
       </c>
-      <c r="AH10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>90.93000000000001</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AQ10" t="n">
-        <v>10.86</v>
+        <v>10.87</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.93</v>
+        <v>10.53</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.789999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>52.36</v>
+        <v>54.07</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.14</v>
+        <v>12.07</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.64</v>
+        <v>8.27</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.79</v>
+        <v>21.07</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BH10" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="BI10" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>4.13</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.76</v>
+        <v>4.83</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="BS10" t="n">
-        <v>75.86</v>
+        <v>73.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>62.07</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>37.93</v>
+        <v>36.67</v>
       </c>
       <c r="BV10" t="n">
-        <v>24.14</v>
+        <v>23.33</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="BX10" t="n">
-        <v>48.28</v>
+        <v>46.67</v>
       </c>
       <c r="BY10" t="n">
         <v>1.89</v>
@@ -4834,34 +4834,34 @@
         <v>1.96</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CE10" t="n">
         <v>1.28</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="CH10" t="n">
         <v>1.58</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK10" t="n">
         <v>1.37</v>
@@ -4870,133 +4870,133 @@
         <v>1.73</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CO10" t="n">
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CT10" t="n">
         <v>3.17</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CX10" t="n">
         <v>1.52</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.45</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="DH10" t="n">
-        <v>98.38</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.59</v>
+        <v>5.76</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="DM10" t="n">
-        <v>52.97</v>
+        <v>54.86</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="DP10" t="n">
         <v>11.1</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.93</v>
+        <v>10.73</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.28</v>
+        <v>7.2</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.52</v>
+        <v>55.3</v>
       </c>
       <c r="DW10" t="n">
         <v>0.1</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.62</v>
+        <v>14</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.130000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.48</v>
+        <v>4.6</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.59</v>
+        <v>19.77</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
         <v>15</v>
@@ -5018,82 +5018,82 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="G11" t="n">
         <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>96.20999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="I11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="K11" t="n">
-        <v>7.64</v>
+        <v>7.47</v>
       </c>
       <c r="L11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="M11" t="n">
-        <v>55.5</v>
+        <v>56.87</v>
       </c>
       <c r="N11" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="O11" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>10.79</v>
+        <v>10.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.21</v>
+        <v>13</v>
       </c>
       <c r="R11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="S11" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="U11" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="V11" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>57.57</v>
+        <v>57.53</v>
       </c>
       <c r="Y11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.57</v>
+        <v>15.13</v>
       </c>
       <c r="AA11" t="n">
-        <v>10.14</v>
+        <v>10.27</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.43</v>
+        <v>4.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.14</v>
+        <v>20.73</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AF11" t="n">
         <v>0.2</v>
@@ -5177,70 +5177,70 @@
         <v>2.53</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.79</v>
+        <v>10.7</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.59</v>
+        <v>4.53</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.52</v>
+        <v>4.53</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="BS11" t="n">
-        <v>79.31</v>
+        <v>80</v>
       </c>
       <c r="BT11" t="n">
-        <v>48.28</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>34.48</v>
+        <v>36.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>20.69</v>
+        <v>23.33</v>
       </c>
       <c r="BW11" t="n">
-        <v>3.45</v>
+        <v>6.67</v>
       </c>
       <c r="BX11" t="n">
-        <v>51.72</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="CC11" t="n">
         <v>2.8</v>
@@ -5249,61 +5249,61 @@
         <v>3.01</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CK11" t="n">
         <v>1.35</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CR11" t="n">
         <v>1.38</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="CT11" t="n">
         <v>3.19</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX11" t="n">
         <v>1.55</v>
@@ -5318,88 +5318,88 @@
         <v>2.21</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="DH11" t="n">
-        <v>83.95999999999999</v>
+        <v>84.36</v>
       </c>
       <c r="DI11" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.13</v>
+        <v>6.1</v>
       </c>
       <c r="DL11" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>49.14</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="DS11" t="n">
         <v>0.17</v>
       </c>
-      <c r="DM11" t="n">
-        <v>48.21</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="DO11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="DP11" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="DQ11" t="n">
-        <v>13.24</v>
-      </c>
-      <c r="DR11" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="DS11" t="n">
-        <v>0.18</v>
-      </c>
       <c r="DT11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52.86</v>
+        <v>53</v>
       </c>
       <c r="DW11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.52</v>
+        <v>12.87</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.449999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.07</v>
+        <v>4.3</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.72</v>
+        <v>19.57</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="EC11" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="12">
@@ -5409,58 +5409,58 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
         <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="G12" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="H12" t="n">
-        <v>94.93000000000001</v>
+        <v>93.33</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="K12" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="M12" t="n">
-        <v>40.21</v>
+        <v>39.47</v>
       </c>
       <c r="N12" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="O12" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>12.79</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.14</v>
+        <v>12.07</v>
       </c>
       <c r="R12" t="n">
         <v>7</v>
       </c>
       <c r="S12" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="T12" t="n">
         <v>2.07</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.71</v>
+        <v>51.8</v>
       </c>
       <c r="Y12" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.07</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.93</v>
+        <v>8</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.5</v>
+        <v>16.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF12" t="n">
         <v>0.13</v>
@@ -5580,67 +5580,67 @@
         <v>2.07</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.45</v>
+        <v>10.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.79</v>
+        <v>4.93</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.66</v>
+        <v>5.67</v>
       </c>
       <c r="BR12" t="n">
-        <v>96.55</v>
+        <v>96.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>82.76000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>68.97</v>
+        <v>66.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>44.83</v>
+        <v>43.33</v>
       </c>
       <c r="BV12" t="n">
-        <v>20.69</v>
+        <v>20</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="BX12" t="n">
-        <v>58.62</v>
+        <v>56.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CB12" t="n">
         <v>4.18</v>
@@ -5664,22 +5664,22 @@
         <v>1.61</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CM12" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CO12" t="n">
         <v>1.17</v>
@@ -5703,73 +5703,73 @@
         <v>1.62</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DB12" t="n">
         <v>1.18</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DE12" t="n">
         <v>0.13</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="DH12" t="n">
-        <v>96.93000000000001</v>
+        <v>96.06</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
         <v>1.97</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.14</v>
+        <v>42.67</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.21</v>
+        <v>13.3</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.72</v>
+        <v>12.67</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.89</v>
+        <v>7.86</v>
       </c>
       <c r="DS12" t="n">
         <v>0.04</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>53.44</v>
+        <v>52.96</v>
       </c>
       <c r="DW12" t="n">
         <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.34</v>
+        <v>14.26</v>
       </c>
       <c r="DY12" t="n">
         <v>9.039999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.31</v>
+        <v>5.24</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.62</v>
+        <v>18.63</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
         <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="G13" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>93.43000000000001</v>
+        <v>90.73</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="J13" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>5.87</v>
       </c>
       <c r="L13" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="M13" t="n">
-        <v>53.43</v>
+        <v>51.93</v>
       </c>
       <c r="N13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O13" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="P13" t="n">
-        <v>11.79</v>
+        <v>11.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.29</v>
+        <v>12.2</v>
       </c>
       <c r="R13" t="n">
-        <v>7.21</v>
+        <v>7.73</v>
       </c>
       <c r="S13" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="T13" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="V13" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>48.5</v>
+        <v>46.73</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.29</v>
+        <v>12.93</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.789999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.21</v>
+        <v>20.93</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AF13" t="n">
         <v>0.2</v>
@@ -5983,70 +5983,70 @@
         <v>1.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BH13" t="n">
-        <v>11.72</v>
+        <v>11.83</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.24</v>
+        <v>5.33</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.17</v>
+        <v>6.2</v>
       </c>
       <c r="BR13" t="n">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="BS13" t="n">
-        <v>86.20999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>68.97</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>51.72</v>
+        <v>50</v>
       </c>
       <c r="BV13" t="n">
-        <v>24.14</v>
+        <v>23.33</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="BX13" t="n">
-        <v>65.52</v>
+        <v>63.33</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="CC13" t="n">
         <v>4.06</v>
@@ -6058,19 +6058,19 @@
         <v>1.26</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CK13" t="n">
         <v>1.32</v>
@@ -6079,7 +6079,7 @@
         <v>1.62</v>
       </c>
       <c r="CM13" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CN13" t="n">
         <v>2.32</v>
@@ -6088,91 +6088,91 @@
         <v>1.15</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CR13" t="n">
         <v>1.38</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CT13" t="n">
         <v>3.15</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CX13" t="n">
         <v>1.51</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.43</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DC13" t="n">
         <v>1.57</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
       <c r="DH13" t="n">
-        <v>94.86</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.79</v>
+        <v>5.74</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="DM13" t="n">
-        <v>54.1</v>
+        <v>53.33</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.55</v>
+        <v>11.33</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.25</v>
+        <v>11.23</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.86</v>
+        <v>8.1</v>
       </c>
       <c r="DS13" t="n">
         <v>0.24</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.83</v>
+        <v>47.93</v>
       </c>
       <c r="DW13" t="n">
         <v>0.04</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.45</v>
+        <v>14.23</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.279999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.17</v>
+        <v>5.14</v>
       </c>
       <c r="EA13" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
         <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
         <v>0.2</v>
@@ -6308,49 +6308,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AH14" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="AI14" t="n">
-        <v>83</v>
+        <v>82.87</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.57</v>
+        <v>5.4</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AN14" t="n">
-        <v>37.43</v>
+        <v>37.4</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.710000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="AR14" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="AS14" t="n">
         <v>11.07</v>
       </c>
-      <c r="AS14" t="n">
-        <v>11.36</v>
-      </c>
       <c r="AT14" t="n">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AV14" t="n">
         <v>0.07000000000000001</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>44.07</v>
+        <v>44</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.57</v>
+        <v>10.73</v>
       </c>
       <c r="BB14" t="n">
-        <v>7</v>
+        <v>7.27</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="BD14" t="n">
-        <v>19.57</v>
+        <v>19.33</v>
       </c>
       <c r="BE14" t="n">
         <v>1.19</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="BH14" t="n">
-        <v>12.97</v>
+        <v>12.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BP14" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.31</v>
+        <v>6.27</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>79.31</v>
+        <v>80</v>
       </c>
       <c r="BU14" t="n">
-        <v>41.38</v>
+        <v>43.33</v>
       </c>
       <c r="BV14" t="n">
-        <v>31.03</v>
+        <v>33.33</v>
       </c>
       <c r="BW14" t="n">
-        <v>3.45</v>
+        <v>6.67</v>
       </c>
       <c r="BX14" t="n">
-        <v>65.52</v>
+        <v>63.33</v>
       </c>
       <c r="BY14" t="n">
         <v>3.05</v>
@@ -6446,31 +6446,31 @@
         <v>3.25</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.29</v>
+        <v>4.31</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.59</v>
+        <v>4.63</v>
       </c>
       <c r="CC14" t="n">
         <v>5.55</v>
       </c>
       <c r="CD14" t="n">
-        <v>6.13</v>
+        <v>6.15</v>
       </c>
       <c r="CE14" t="n">
         <v>1.26</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.56</v>
@@ -6482,7 +6482,7 @@
         <v>1.53</v>
       </c>
       <c r="CM14" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CN14" t="n">
         <v>2.55</v>
@@ -6491,28 +6491,28 @@
         <v>1.15</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CR14" t="n">
         <v>1.36</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CT14" t="n">
         <v>3.25</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
@@ -6526,10 +6526,10 @@
         <v>1.18</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="DE14" t="n">
         <v>0.1</v>
@@ -6538,73 +6538,73 @@
         <v>0.76</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="DH14" t="n">
-        <v>87.06999999999999</v>
+        <v>86.87</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.1</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.79</v>
+        <v>5.7</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM14" t="n">
-        <v>42.07</v>
+        <v>41.9</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="DP14" t="n">
         <v>10.27</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.35</v>
+        <v>10.27</v>
       </c>
       <c r="DR14" t="n">
-        <v>10.62</v>
+        <v>10.5</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>45.62</v>
+        <v>45.54</v>
       </c>
       <c r="DW14" t="n">
         <v>0.04</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.51</v>
+        <v>12.53</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.279999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.24</v>
+        <v>4.17</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.97</v>
+        <v>17.9</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="15">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" t="n">
         <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
         <v>0.13</v>
@@ -6704,22 +6704,22 @@
         <v>1.93</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AI15" t="n">
-        <v>103.29</v>
+        <v>102.8</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AL15" t="n">
         <v>4</v>
@@ -6728,28 +6728,28 @@
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>47.14</v>
+        <v>46.33</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.43</v>
+        <v>12.53</v>
       </c>
       <c r="AR15" t="n">
-        <v>10.93</v>
+        <v>11.07</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.93</v>
+        <v>7.53</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AV15" t="n">
         <v>0.07000000000000001</v>
@@ -6761,82 +6761,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>47.86</v>
+        <v>48.6</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.71</v>
+        <v>10.93</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.93</v>
+        <v>4.13</v>
       </c>
       <c r="BD15" t="n">
-        <v>19.79</v>
+        <v>20.33</v>
       </c>
       <c r="BE15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO15" t="n">
         <v>1.3</v>
       </c>
-      <c r="BF15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.24</v>
-      </c>
       <c r="BP15" t="n">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.07</v>
+        <v>4.03</v>
       </c>
       <c r="BR15" t="n">
-        <v>96.55</v>
+        <v>96.67</v>
       </c>
       <c r="BS15" t="n">
-        <v>65.52</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>51.72</v>
+        <v>53.33</v>
       </c>
       <c r="BU15" t="n">
-        <v>41.38</v>
+        <v>43.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
       <c r="BW15" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="BX15" t="n">
-        <v>51.72</v>
+        <v>53.33</v>
       </c>
       <c r="BY15" t="n">
         <v>1.91</v>
@@ -6845,31 +6845,31 @@
         <v>1.96</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.01</v>
+        <v>2.91</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="CE15" t="n">
         <v>1.33</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CG15" t="n">
         <v>3.07</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.75</v>
@@ -6878,31 +6878,31 @@
         <v>1.44</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CU15" t="n">
         <v>1.48</v>
@@ -6923,28 +6923,28 @@
         <v>2.42</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="DH15" t="n">
-        <v>97.28</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
@@ -6956,55 +6956,55 @@
         <v>4.14</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.96</v>
+        <v>47.53</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.14</v>
+        <v>13.16</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.41</v>
+        <v>10.5</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.41</v>
+        <v>7.23</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>49.86</v>
+        <v>50.16</v>
       </c>
       <c r="DW15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.83</v>
+        <v>11.9</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.52</v>
+        <v>7.5</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.31</v>
+        <v>4.4</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.14</v>
+        <v>19.43</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC15" t="n">
         <v>1.76</v>
@@ -7017,94 +7017,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="F16" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="G16" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="H16" t="n">
-        <v>101.79</v>
+        <v>100.07</v>
       </c>
       <c r="I16" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="K16" t="n">
-        <v>9.359999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="M16" t="n">
-        <v>65.86</v>
+        <v>64.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="O16" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>11.57</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.36</v>
+        <v>11.4</v>
       </c>
       <c r="R16" t="n">
-        <v>6</v>
+        <v>6.13</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>52.93</v>
+        <v>52.53</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>18.5</v>
+        <v>18.27</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.57</v>
+        <v>12.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.93</v>
+        <v>5.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>22.07</v>
+        <v>22.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF16" t="n">
         <v>0.4</v>
@@ -7188,70 +7188,70 @@
         <v>1.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.69</v>
+        <v>3.77</v>
       </c>
       <c r="BH16" t="n">
-        <v>12.07</v>
+        <v>11.97</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.69</v>
+        <v>3.77</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BM16" t="n">
         <v>0.83</v>
       </c>
       <c r="BN16" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="BO16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>80</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>76.67</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY16" t="n">
         <v>1.62</v>
       </c>
-      <c r="BP16" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>96.55</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>79.31</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>75.86</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>55.17</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>27.59</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>68.97</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>1.66</v>
-      </c>
       <c r="BZ16" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.63</v>
+        <v>4.73</v>
       </c>
       <c r="CC16" t="n">
         <v>2.36</v>
@@ -7263,13 +7263,13 @@
         <v>1.24</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CI16" t="n">
         <v>2.42</v>
@@ -7278,13 +7278,13 @@
         <v>1.53</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CL16" t="n">
         <v>1.51</v>
       </c>
       <c r="CM16" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CN16" t="n">
         <v>2.55</v>
@@ -7293,25 +7293,25 @@
         <v>1.13</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CR16" t="n">
         <v>1.37</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CT16" t="n">
         <v>3.16</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CW16" t="n">
         <v>1.57</v>
@@ -7335,82 +7335,82 @@
         <v>1.52</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="DF16" t="n">
         <v>1</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="DH16" t="n">
-        <v>96.52</v>
+        <v>95.84</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DK16" t="n">
-        <v>7.79</v>
+        <v>7.73</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DM16" t="n">
-        <v>56.24</v>
+        <v>55.74</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="DO16" t="n">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.35</v>
+        <v>12.54</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.45</v>
+        <v>11.46</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.79</v>
+        <v>6.83</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>50.9</v>
+        <v>50.76</v>
       </c>
       <c r="DW16" t="n">
         <v>0.04</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.76</v>
+        <v>15.74</v>
       </c>
       <c r="DY16" t="n">
         <v>10</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.76</v>
+        <v>5.74</v>
       </c>
       <c r="EA16" t="n">
-        <v>23</v>
+        <v>23.04</v>
       </c>
       <c r="EB16" t="n">
         <v>1.8</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="17">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>0.2</v>
@@ -7510,52 +7510,52 @@
         <v>1.53</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="AI17" t="n">
-        <v>89.5</v>
+        <v>88</v>
       </c>
       <c r="AJ17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.57</v>
+        <v>4.47</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AN17" t="n">
-        <v>48.21</v>
+        <v>46</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>12.07</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.36</v>
+        <v>13.67</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.359999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AV17" t="n">
         <v>0.07000000000000001</v>
@@ -7567,82 +7567,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>47.29</v>
+        <v>47.67</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.79</v>
+        <v>10.73</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.57</v>
+        <v>7.47</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.64</v>
+        <v>20.47</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="BH17" t="n">
-        <v>11.31</v>
+        <v>11.23</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BN17" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.62</v>
+        <v>4.63</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.1</v>
+        <v>6.03</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>86.20999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>58.62</v>
+        <v>60</v>
       </c>
       <c r="BU17" t="n">
-        <v>37.93</v>
+        <v>40</v>
       </c>
       <c r="BV17" t="n">
-        <v>27.59</v>
+        <v>30</v>
       </c>
       <c r="BW17" t="n">
-        <v>10.34</v>
+        <v>13.33</v>
       </c>
       <c r="BX17" t="n">
-        <v>65.52</v>
+        <v>66.67</v>
       </c>
       <c r="BY17" t="n">
         <v>2.35</v>
@@ -7651,28 +7651,28 @@
         <v>2.38</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.92</v>
+        <v>4.02</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.14</v>
+        <v>4.27</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.4</v>
+        <v>3.87</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.65</v>
+        <v>4.13</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CI17" t="n">
         <v>2.36</v>
@@ -7696,25 +7696,25 @@
         <v>1.18</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CT17" t="n">
         <v>3.19</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CW17" t="n">
         <v>1.59</v>
@@ -7735,49 +7735,49 @@
         <v>1.2</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="DH17" t="n">
-        <v>89.72</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.38</v>
+        <v>5.3</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM17" t="n">
-        <v>50.69</v>
+        <v>49.5</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.17</v>
+        <v>12.2</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.14</v>
+        <v>13.3</v>
       </c>
       <c r="DR17" t="n">
         <v>8.9</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>48.45</v>
+        <v>48.6</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.9</v>
+        <v>13.77</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.31</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.69</v>
+        <v>20.6</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
+++ b/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
@@ -3096,7 +3096,7 @@
         <v>-0.13</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AL6" t="n">
         <v>4.27</v>
@@ -3108,7 +3108,7 @@
         <v>33.67</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="AP6" t="n">
         <v>1.33</v>
@@ -3141,13 +3141,13 @@
         <v>41</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA6" t="n">
-        <v>11</v>
+        <v>10.93</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.47</v>
+        <v>7.4</v>
       </c>
       <c r="BC6" t="n">
         <v>3.53</v>
@@ -3327,7 +3327,7 @@
         <v>-0.03</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="DK6" t="n">
         <v>4.77</v>
@@ -3339,7 +3339,7 @@
         <v>39.43</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="DO6" t="n">
         <v>1.53</v>
@@ -3366,13 +3366,13 @@
         <v>41.86</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.04</v>
+        <v>12</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.4</v>
+        <v>7.36</v>
       </c>
       <c r="DZ6" t="n">
         <v>4.63</v>

--- a/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
+++ b/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
@@ -3466,10 +3466,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.53</v>
+        <v>5.6</v>
       </c>
       <c r="AB7" t="n">
         <v>3.27</v>
@@ -3772,10 +3772,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.74</v>
+        <v>8.77</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.33</v>
+        <v>5.36</v>
       </c>
       <c r="DZ7" t="n">
         <v>3.4</v>
@@ -4756,19 +4756,19 @@
         <v>0.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.07</v>
+        <v>12.13</v>
       </c>
       <c r="BB10" t="n">
         <v>8.27</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="BD10" t="n">
         <v>21.07</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BF10" t="n">
         <v>2.2</v>
@@ -4981,13 +4981,13 @@
         <v>0.1</v>
       </c>
       <c r="DX10" t="n">
-        <v>14</v>
+        <v>14.03</v>
       </c>
       <c r="DY10" t="n">
         <v>9.4</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="EA10" t="n">
         <v>19.77</v>
@@ -5078,10 +5078,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>15.13</v>
+        <v>15.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>10.27</v>
+        <v>10.33</v>
       </c>
       <c r="AB11" t="n">
         <v>4.87</v>
@@ -5090,7 +5090,7 @@
         <v>20.73</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE11" t="n">
         <v>1.33</v>
@@ -5384,10 +5384,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.87</v>
+        <v>12.9</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.57</v>
+        <v>8.6</v>
       </c>
       <c r="DZ11" t="n">
         <v>4.3</v>
@@ -7083,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>52.53</v>
+        <v>52.6</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -7389,7 +7389,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>50.76</v>
+        <v>50.8</v>
       </c>
       <c r="DW16" t="n">
         <v>0.04</v>
@@ -7567,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>47.67</v>
+        <v>47.6</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.2</v>
@@ -7792,7 +7792,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>48.6</v>
+        <v>48.57</v>
       </c>
       <c r="DW17" t="n">
         <v>0.13</v>

--- a/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
+++ b/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
@@ -1532,10 +1532,10 @@
         <v>0.13</v>
       </c>
       <c r="BA2" t="n">
-        <v>14.07</v>
+        <v>14.13</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.27</v>
+        <v>9.33</v>
       </c>
       <c r="BC2" t="n">
         <v>4.8</v>
@@ -1544,7 +1544,7 @@
         <v>20.67</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BF2" t="n">
         <v>1.73</v>
@@ -1757,10 +1757,10 @@
         <v>0.1</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.17</v>
+        <v>15.2</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="DZ2" t="n">
         <v>5.46</v>
@@ -1769,7 +1769,7 @@
         <v>24.74</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="EC2" t="n">
         <v>1.66</v>
@@ -1797,7 +1797,7 @@
         <v>1.27</v>
       </c>
       <c r="G3" t="n">
-        <v>2.67</v>
+        <v>2.93</v>
       </c>
       <c r="H3" t="n">
         <v>98.06999999999999</v>
@@ -1812,7 +1812,7 @@
         <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="M3" t="n">
         <v>45.13</v>
@@ -1821,7 +1821,7 @@
         <v>0.73</v>
       </c>
       <c r="O3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="P3" t="n">
         <v>13.2</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>49.2</v>
+        <v>49.13</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1980,10 +1980,10 @@
         <v>1.33</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.13</v>
+        <v>4.27</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.3</v>
+        <v>4.47</v>
       </c>
       <c r="BR3" t="n">
         <v>96.67</v>
@@ -2109,7 +2109,7 @@
         <v>1.1</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="DH3" t="n">
         <v>90.73999999999999</v>
@@ -2124,7 +2124,7 @@
         <v>3.96</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DM3" t="n">
         <v>38.73</v>
@@ -2133,7 +2133,7 @@
         <v>0.66</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DP3" t="n">
         <v>12.4</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.64</v>
+        <v>44.6</v>
       </c>
       <c r="DW3" t="n">
         <v>0.04</v>
@@ -2281,7 +2281,7 @@
         <v>0.93</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AI4" t="n">
         <v>106.07</v>
@@ -2296,7 +2296,7 @@
         <v>7.47</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="AN4" t="n">
         <v>66.27</v>
@@ -2305,7 +2305,7 @@
         <v>0.2</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AQ4" t="n">
         <v>8.6</v>
@@ -2338,10 +2338,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="BA4" t="n">
-        <v>16.67</v>
+        <v>16.73</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.87</v>
+        <v>10.93</v>
       </c>
       <c r="BC4" t="n">
         <v>5.8</v>
@@ -2383,10 +2383,10 @@
         <v>1.73</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.53</v>
+        <v>5.17</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.23</v>
+        <v>5.07</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2512,7 +2512,7 @@
         <v>0.6</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.64</v>
+        <v>3.54</v>
       </c>
       <c r="DH4" t="n">
         <v>108.07</v>
@@ -2527,7 +2527,7 @@
         <v>7.74</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DM4" t="n">
         <v>76.90000000000001</v>
@@ -2536,7 +2536,7 @@
         <v>0.16</v>
       </c>
       <c r="DO4" t="n">
-        <v>4.04</v>
+        <v>3.74</v>
       </c>
       <c r="DP4" t="n">
         <v>8.44</v>
@@ -2563,10 +2563,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DX4" t="n">
-        <v>18.33</v>
+        <v>18.37</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.93</v>
+        <v>11.96</v>
       </c>
       <c r="DZ4" t="n">
         <v>6.4</v>
@@ -2663,16 +2663,16 @@
         <v>12.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.07</v>
+        <v>8</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.2</v>
+        <v>21.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE5" t="n">
         <v>1.27</v>
@@ -2969,13 +2969,13 @@
         <v>11.34</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.14</v>
+        <v>7.1</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.4</v>
+        <v>21.44</v>
       </c>
       <c r="EB5" t="n">
         <v>1.34</v>
@@ -3063,10 +3063,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.07</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.33</v>
+        <v>7.27</v>
       </c>
       <c r="AB6" t="n">
         <v>5.73</v>
@@ -3096,7 +3096,7 @@
         <v>-0.13</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AL6" t="n">
         <v>4.27</v>
@@ -3108,7 +3108,7 @@
         <v>33.67</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="AP6" t="n">
         <v>1.33</v>
@@ -3144,10 +3144,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.93</v>
+        <v>11.07</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.4</v>
+        <v>7.53</v>
       </c>
       <c r="BC6" t="n">
         <v>3.53</v>
@@ -3156,10 +3156,10 @@
         <v>20.13</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="BG6" t="n">
         <v>2.97</v>
@@ -3327,7 +3327,7 @@
         <v>-0.03</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="DK6" t="n">
         <v>4.77</v>
@@ -3339,7 +3339,7 @@
         <v>39.43</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="DO6" t="n">
         <v>1.53</v>
@@ -3369,10 +3369,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DX6" t="n">
-        <v>12</v>
+        <v>12.04</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.36</v>
+        <v>7.4</v>
       </c>
       <c r="DZ6" t="n">
         <v>4.63</v>
@@ -3384,7 +3384,7 @@
         <v>1.38</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
@@ -3812,7 +3812,7 @@
         <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="H8" t="n">
         <v>98.47</v>
@@ -3827,7 +3827,7 @@
         <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="M8" t="n">
         <v>54.93</v>
@@ -3836,7 +3836,7 @@
         <v>0.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
         <v>12</v>
@@ -3923,7 +3923,7 @@
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.6</v>
+        <v>11.53</v>
       </c>
       <c r="AS8" t="n">
         <v>6.6</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>50.13</v>
+        <v>50.2</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -3953,16 +3953,16 @@
         <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.07</v>
+        <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
         <v>19.47</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BF8" t="n">
         <v>1.93</v>
@@ -3995,10 +3995,10 @@
         <v>1.07</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.03</v>
+        <v>4.67</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.07</v>
+        <v>3.9</v>
       </c>
       <c r="BR8" t="n">
         <v>90</v>
@@ -4124,7 +4124,7 @@
         <v>1.33</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="DH8" t="n">
         <v>97.27</v>
@@ -4139,7 +4139,7 @@
         <v>4.96</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DM8" t="n">
         <v>46.7</v>
@@ -4148,13 +4148,13 @@
         <v>0.7</v>
       </c>
       <c r="DO8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="DP8" t="n">
         <v>11.5</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.54</v>
+        <v>10.5</v>
       </c>
       <c r="DR8" t="n">
         <v>6.56</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.4</v>
+        <v>50.44</v>
       </c>
       <c r="DW8" t="n">
         <v>0.1</v>
@@ -4178,16 +4178,16 @@
         <v>11.37</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.47</v>
+        <v>7.44</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="EA8" t="n">
         <v>18.2</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC8" t="n">
         <v>1.93</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.47</v>
+        <v>45.53</v>
       </c>
       <c r="Y9" t="n">
         <v>0.07000000000000001</v>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>40.4</v>
+        <v>40.33</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.07000000000000001</v>
@@ -4675,16 +4675,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.93</v>
+        <v>15.87</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.53</v>
+        <v>10.47</v>
       </c>
       <c r="AB10" t="n">
         <v>5.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.47</v>
+        <v>18.4</v>
       </c>
       <c r="AD10" t="n">
         <v>1.81</v>
@@ -4750,16 +4750,16 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>54.07</v>
+        <v>54.13</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.13</v>
+        <v>12.07</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC10" t="n">
         <v>3.87</v>
@@ -4768,7 +4768,7 @@
         <v>21.07</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BF10" t="n">
         <v>2.2</v>
@@ -4975,22 +4975,22 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.3</v>
+        <v>55.33</v>
       </c>
       <c r="DW10" t="n">
         <v>0.1</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.03</v>
+        <v>13.97</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.4</v>
+        <v>9.34</v>
       </c>
       <c r="DZ10" t="n">
         <v>4.64</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.77</v>
+        <v>19.74</v>
       </c>
       <c r="EB10" t="n">
         <v>1.61</v>
@@ -5451,7 +5451,7 @@
         <v>1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
+        <v>12.93</v>
       </c>
       <c r="Q12" t="n">
         <v>12.07</v>
@@ -5763,7 +5763,7 @@
         <v>2.03</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.3</v>
+        <v>13.26</v>
       </c>
       <c r="DQ12" t="n">
         <v>12.67</v>
@@ -5854,7 +5854,7 @@
         <v>2.87</v>
       </c>
       <c r="P13" t="n">
-        <v>11.33</v>
+        <v>11.6</v>
       </c>
       <c r="Q13" t="n">
         <v>12.2</v>
@@ -5878,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>46.73</v>
+        <v>46.67</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.33</v>
+        <v>3.47</v>
       </c>
       <c r="AI13" t="n">
         <v>96.2</v>
@@ -5923,7 +5923,7 @@
         <v>5.6</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="AN13" t="n">
         <v>54.73</v>
@@ -5932,7 +5932,7 @@
         <v>0.33</v>
       </c>
       <c r="AP13" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ13" t="n">
         <v>11.33</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>49.13</v>
+        <v>49.2</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.07000000000000001</v>
@@ -5968,10 +5968,10 @@
         <v>15.53</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.73</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.8</v>
+        <v>5.73</v>
       </c>
       <c r="BD13" t="n">
         <v>18.87</v>
@@ -6010,10 +6010,10 @@
         <v>1.4</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.33</v>
+        <v>5.47</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.2</v>
+        <v>6.37</v>
       </c>
       <c r="BR13" t="n">
         <v>93.33</v>
@@ -6139,7 +6139,7 @@
         <v>1.13</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.16</v>
+        <v>3.24</v>
       </c>
       <c r="DH13" t="n">
         <v>93.45999999999999</v>
@@ -6154,7 +6154,7 @@
         <v>5.74</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DM13" t="n">
         <v>53.33</v>
@@ -6163,10 +6163,10 @@
         <v>0.33</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.33</v>
+        <v>11.46</v>
       </c>
       <c r="DQ13" t="n">
         <v>11.23</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.93</v>
+        <v>47.94</v>
       </c>
       <c r="DW13" t="n">
         <v>0.04</v>
@@ -6193,10 +6193,10 @@
         <v>14.23</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.1</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="EA13" t="n">
         <v>19.9</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.73</v>
+        <v>10.87</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.27</v>
+        <v>7.4</v>
       </c>
       <c r="BC14" t="n">
         <v>3.47</v>
@@ -6380,7 +6380,7 @@
         <v>19.33</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BF14" t="n">
         <v>1.2</v>
@@ -6589,10 +6589,10 @@
         <v>0.04</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.53</v>
+        <v>12.6</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.369999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="DZ14" t="n">
         <v>4.17</v>
@@ -6601,7 +6601,7 @@
         <v>17.9</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="EC14" t="n">
         <v>1.34</v>
@@ -6761,16 +6761,16 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>48.6</v>
+        <v>48.47</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.93</v>
+        <v>11.07</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.8</v>
+        <v>6.93</v>
       </c>
       <c r="BC15" t="n">
         <v>4.13</v>
@@ -6779,7 +6779,7 @@
         <v>20.33</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BF15" t="n">
         <v>1.6</v>
@@ -6986,16 +6986,16 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>50.16</v>
+        <v>50.1</v>
       </c>
       <c r="DW15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.9</v>
+        <v>11.97</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.5</v>
+        <v>7.56</v>
       </c>
       <c r="DZ15" t="n">
         <v>4.4</v>
@@ -7098,7 +7098,7 @@
         <v>5.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>22.2</v>
+        <v>22.13</v>
       </c>
       <c r="AD16" t="n">
         <v>2.02</v>
@@ -7164,16 +7164,16 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>49</v>
+        <v>49.07</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA16" t="n">
-        <v>13.2</v>
+        <v>13.27</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.6</v>
+        <v>7.67</v>
       </c>
       <c r="BC16" t="n">
         <v>5.6</v>
@@ -7389,22 +7389,22 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>50.8</v>
+        <v>50.84</v>
       </c>
       <c r="DW16" t="n">
         <v>0.04</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.74</v>
+        <v>15.77</v>
       </c>
       <c r="DY16" t="n">
-        <v>10</v>
+        <v>10.04</v>
       </c>
       <c r="DZ16" t="n">
         <v>5.74</v>
       </c>
       <c r="EA16" t="n">
-        <v>23.04</v>
+        <v>23</v>
       </c>
       <c r="EB16" t="n">
         <v>1.8</v>

--- a/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
+++ b/data/teams/leagues/Averages_Norway_Eliteserien_2025.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
